--- a/length_pipeline_results.xlsx
+++ b/length_pipeline_results.xlsx
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.3876923076923077</v>
+        <v>0.4</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.3876923076923077</v>
+        <v>0.4</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>0</v>
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5753846153846154</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5753846153846154</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>0</v>
@@ -626,10 +626,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5692307692307692</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5692307692307692</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>0</v>
@@ -642,10 +642,10 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5661538461538461</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5661538461538461</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5753846153846154</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5753846153846154</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>0</v>
@@ -674,10 +674,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.3876923076923077</v>
+        <v>0.4</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.3876923076923077</v>
+        <v>0.4</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>0</v>
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5753846153846154</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5753846153846154</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>0</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5723076923076923</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5723076923076923</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>0</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5661538461538461</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5661538461538461</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>0</v>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5753846153846154</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5753846153846154</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>0</v>
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.3876923076923077</v>
+        <v>0.4</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.3876923076923077</v>
+        <v>0.4</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>0</v>
@@ -770,10 +770,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5723076923076923</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5723076923076923</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>0</v>
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5692307692307692</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5692307692307692</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>0</v>
@@ -802,10 +802,10 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5661538461538461</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.6</v>
+        <v>0.5661538461538461</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>0</v>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5784615384615385</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.6030769230769231</v>
+        <v>0.5784615384615385</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>0</v>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>0.5593846153846154</v>
+        <v>0.5374358974358974</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>0.5593846153846154</v>
+        <v>0.5374358974358974</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>0</v>
@@ -846,7 +846,7 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Global truncation cap: 266 tokens  |  [Truncate only] mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>Global truncation cap: 265 tokens  |  [Truncate only] mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -949,19 +949,19 @@
         <v>758</v>
       </c>
       <c r="E2" s="13" t="n">
-        <v>258.7</v>
+        <v>257.2</v>
       </c>
       <c r="F2" s="13" t="n">
-        <v>30.1</v>
+        <v>31.7</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H2" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I2" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3">
@@ -976,7 +976,7 @@
         <v>758</v>
       </c>
       <c r="E3" s="17" t="n">
-        <v>263.7</v>
+        <v>262.8</v>
       </c>
       <c r="F3" s="17" t="n">
         <v>7.2</v>
@@ -985,10 +985,10 @@
         <v>211</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4">
@@ -1008,22 +1008,22 @@
         </is>
       </c>
       <c r="D4" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="5">
@@ -1038,19 +1038,19 @@
         <v>81</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G5" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I5" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6">
@@ -1065,19 +1065,19 @@
         <v>81</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7">
@@ -1089,22 +1089,22 @@
         </is>
       </c>
       <c r="D7" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8">
@@ -1127,19 +1127,19 @@
         <v>758</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>257.7</v>
+        <v>257.1</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9">
@@ -1154,19 +1154,19 @@
         <v>250</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>180.1</v>
+        <v>177.4</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>79.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>185.5</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -1181,19 +1181,19 @@
         <v>508</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>263.6</v>
+        <v>263</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -1213,22 +1213,22 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12">
@@ -1243,19 +1243,19 @@
         <v>81</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13">
@@ -1270,19 +1270,19 @@
         <v>81</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14">
@@ -1294,22 +1294,22 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15">
@@ -1332,7 +1332,7 @@
         <v>758</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>257.4</v>
+        <v>256.2</v>
       </c>
       <c r="F15" s="13" t="n">
         <v>33.4</v>
@@ -1341,10 +1341,10 @@
         <v>32</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16">
@@ -1359,19 +1359,19 @@
         <v>379</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>185.9</v>
+        <v>181.4</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>80.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G16" s="21" t="n">
         <v>51</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17">
@@ -1386,19 +1386,19 @@
         <v>379</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>263.9</v>
+        <v>262.9</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18">
@@ -1418,22 +1418,22 @@
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="19">
@@ -1448,19 +1448,19 @@
         <v>81</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F19" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G19" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I19" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20">
@@ -1475,19 +1475,19 @@
         <v>81</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
@@ -1499,22 +1499,22 @@
         </is>
       </c>
       <c r="D21" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F21" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22">
@@ -1537,19 +1537,19 @@
         <v>758</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>257.7</v>
+        <v>256.5</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>32.7</v>
+        <v>33.3</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>32</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23">
@@ -1564,19 +1564,19 @@
         <v>508</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>182.8</v>
+        <v>182.5</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>80.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>195</v>
+        <v>192.5</v>
       </c>
     </row>
     <row r="24">
@@ -1591,19 +1591,19 @@
         <v>250</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>263.7</v>
+        <v>262.8</v>
       </c>
       <c r="F24" s="17" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="26">
@@ -1653,19 +1653,19 @@
         <v>81</v>
       </c>
       <c r="E26" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G26" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I26" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27">
@@ -1680,19 +1680,19 @@
         <v>81</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I27" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28">
@@ -1704,22 +1704,22 @@
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F28" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G28" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29">
@@ -1742,19 +1742,19 @@
         <v>758</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>256.9</v>
+        <v>256.4</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>34.4</v>
+        <v>33.9</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>32</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30">
@@ -1769,19 +1769,19 @@
         <v>758</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>183.5</v>
+        <v>181.6</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>79.8</v>
+        <v>79</v>
       </c>
       <c r="G30" s="21" t="n">
         <v>51</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31">
@@ -1801,22 +1801,22 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="32">
@@ -1831,19 +1831,19 @@
         <v>81</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G32" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H32" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="33">
@@ -1858,19 +1858,19 @@
         <v>81</v>
       </c>
       <c r="E33" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H33" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I33" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34">
@@ -1882,22 +1882,22 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F34" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35">
@@ -1920,19 +1920,19 @@
         <v>508</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>257.8</v>
+        <v>257.4</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>32</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36">
@@ -1947,19 +1947,19 @@
         <v>250</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>257.4</v>
+        <v>255.9</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>28.8</v>
+        <v>33.1</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I36" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="37">
@@ -1974,7 +1974,7 @@
         <v>758</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>263.8</v>
+        <v>262.9</v>
       </c>
       <c r="F37" s="17" t="n">
         <v>7</v>
@@ -1983,10 +1983,10 @@
         <v>211</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38">
@@ -2006,22 +2006,22 @@
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="39">
@@ -2036,19 +2036,19 @@
         <v>81</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G39" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I39" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="40">
@@ -2063,19 +2063,19 @@
         <v>81</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41">
@@ -2087,22 +2087,22 @@
         </is>
       </c>
       <c r="D41" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E41" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F41" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="42">
@@ -2125,19 +2125,19 @@
         <v>508</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>257.1</v>
+        <v>258</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>34.5</v>
+        <v>31.5</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>32</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="43">
@@ -2152,19 +2152,19 @@
         <v>250</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>252.9</v>
+        <v>256.3</v>
       </c>
       <c r="F43" s="20" t="n">
-        <v>39.2</v>
+        <v>30.7</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I43" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44">
@@ -2179,19 +2179,19 @@
         <v>250</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>190</v>
+        <v>178.1</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>78.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>225</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45">
@@ -2206,19 +2206,19 @@
         <v>508</v>
       </c>
       <c r="E45" s="17" t="n">
-        <v>264.1</v>
+        <v>262.8</v>
       </c>
       <c r="F45" s="17" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I45" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="46">
@@ -2238,22 +2238,22 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="47">
@@ -2268,19 +2268,19 @@
         <v>81</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F47" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G47" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I47" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="48">
@@ -2295,19 +2295,19 @@
         <v>81</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49">
@@ -2319,22 +2319,22 @@
         </is>
       </c>
       <c r="D49" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E49" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F49" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G49" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="50">
@@ -2357,19 +2357,19 @@
         <v>508</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>257.9</v>
+        <v>258.5</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>32.2</v>
+        <v>28.3</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>36</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51">
@@ -2384,19 +2384,19 @@
         <v>250</v>
       </c>
       <c r="E51" s="20" t="n">
-        <v>257.2</v>
+        <v>254.9</v>
       </c>
       <c r="F51" s="20" t="n">
-        <v>28.5</v>
+        <v>33</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I51" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="52">
@@ -2411,19 +2411,19 @@
         <v>379</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>178.3</v>
+        <v>188.4</v>
       </c>
       <c r="F52" s="22" t="n">
-        <v>80.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>178</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53">
@@ -2438,19 +2438,19 @@
         <v>379</v>
       </c>
       <c r="E53" s="17" t="n">
-        <v>264.1</v>
+        <v>263.1</v>
       </c>
       <c r="F53" s="17" t="n">
         <v>6.1</v>
       </c>
       <c r="G53" s="16" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I53" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54">
@@ -2470,22 +2470,22 @@
         </is>
       </c>
       <c r="D54" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="55">
@@ -2500,19 +2500,19 @@
         <v>81</v>
       </c>
       <c r="E55" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F55" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G55" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I55" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="56">
@@ -2527,19 +2527,19 @@
         <v>81</v>
       </c>
       <c r="E56" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F56" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G56" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H56" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I56" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57">
@@ -2551,22 +2551,22 @@
         </is>
       </c>
       <c r="D57" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E57" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F57" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G57" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I57" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="58">
@@ -2589,19 +2589,19 @@
         <v>508</v>
       </c>
       <c r="E58" s="13" t="n">
-        <v>258.3</v>
+        <v>257</v>
       </c>
       <c r="F58" s="13" t="n">
-        <v>31</v>
+        <v>31.9</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I58" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="59">
@@ -2616,19 +2616,19 @@
         <v>250</v>
       </c>
       <c r="E59" s="20" t="n">
-        <v>254.3</v>
+        <v>255</v>
       </c>
       <c r="F59" s="20" t="n">
-        <v>37.8</v>
+        <v>33.5</v>
       </c>
       <c r="G59" s="19" t="n">
         <v>61</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I59" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="60">
@@ -2643,19 +2643,19 @@
         <v>508</v>
       </c>
       <c r="E60" s="22" t="n">
-        <v>179</v>
+        <v>181.3</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>79.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G60" s="21" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H60" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I60" s="22" t="n">
-        <v>173.5</v>
+        <v>186.5</v>
       </c>
     </row>
     <row r="61">
@@ -2670,19 +2670,19 @@
         <v>250</v>
       </c>
       <c r="E61" s="17" t="n">
-        <v>263.3</v>
+        <v>262.3</v>
       </c>
       <c r="F61" s="17" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="G61" s="16" t="n">
         <v>215</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="62">
@@ -2702,22 +2702,22 @@
         </is>
       </c>
       <c r="D62" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E62" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F62" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I62" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="63">
@@ -2732,19 +2732,19 @@
         <v>81</v>
       </c>
       <c r="E63" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F63" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G63" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I63" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="64">
@@ -2759,19 +2759,19 @@
         <v>81</v>
       </c>
       <c r="E64" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F64" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G64" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H64" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I64" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="65">
@@ -2783,22 +2783,22 @@
         </is>
       </c>
       <c r="D65" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E65" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F65" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G65" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I65" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="66">
@@ -2821,19 +2821,19 @@
         <v>508</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>257.7</v>
+        <v>256.8</v>
       </c>
       <c r="F66" s="13" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G66" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="G66" s="12" t="n">
-        <v>36</v>
-      </c>
       <c r="H66" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I66" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="67">
@@ -2848,19 +2848,19 @@
         <v>250</v>
       </c>
       <c r="E67" s="20" t="n">
-        <v>254.1</v>
+        <v>253.2</v>
       </c>
       <c r="F67" s="20" t="n">
-        <v>36.1</v>
+        <v>36.3</v>
       </c>
       <c r="G67" s="19" t="n">
         <v>50</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I67" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="68">
@@ -2875,19 +2875,19 @@
         <v>758</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>182.7</v>
+        <v>183.5</v>
       </c>
       <c r="F68" s="22" t="n">
         <v>79.7</v>
       </c>
       <c r="G68" s="21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H68" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I68" s="22" t="n">
-        <v>187.5</v>
+        <v>194.5</v>
       </c>
     </row>
     <row r="69">
@@ -2907,22 +2907,22 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F69" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I69" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="70">
@@ -2937,19 +2937,19 @@
         <v>81</v>
       </c>
       <c r="E70" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F70" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G70" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="71">
@@ -2964,19 +2964,19 @@
         <v>81</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F71" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G71" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H71" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I71" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="72">
@@ -2988,22 +2988,22 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E72" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F72" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G72" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I72" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73">
@@ -3026,19 +3026,19 @@
         <v>379</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>259.6</v>
+        <v>257.2</v>
       </c>
       <c r="F73" s="13" t="n">
-        <v>27.1</v>
+        <v>32.9</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I73" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="74">
@@ -3053,19 +3053,19 @@
         <v>379</v>
       </c>
       <c r="E74" s="20" t="n">
-        <v>255.3</v>
+        <v>252.3</v>
       </c>
       <c r="F74" s="20" t="n">
-        <v>34.1</v>
+        <v>36.9</v>
       </c>
       <c r="G74" s="19" t="n">
         <v>72</v>
       </c>
       <c r="H74" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I74" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="75">
@@ -3080,19 +3080,19 @@
         <v>758</v>
       </c>
       <c r="E75" s="17" t="n">
-        <v>263.8</v>
+        <v>262.8</v>
       </c>
       <c r="F75" s="17" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="G75" s="16" t="n">
         <v>211</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I75" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="76">
@@ -3112,22 +3112,22 @@
         </is>
       </c>
       <c r="D76" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F76" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I76" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="77">
@@ -3142,19 +3142,19 @@
         <v>81</v>
       </c>
       <c r="E77" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F77" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G77" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H77" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I77" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="78">
@@ -3169,19 +3169,19 @@
         <v>81</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F78" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G78" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H78" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I78" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="79">
@@ -3193,22 +3193,22 @@
         </is>
       </c>
       <c r="D79" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E79" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F79" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G79" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H79" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I79" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="80">
@@ -3231,19 +3231,19 @@
         <v>379</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>256.4</v>
+        <v>254</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>34.3</v>
+        <v>38.8</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="81">
@@ -3258,19 +3258,19 @@
         <v>379</v>
       </c>
       <c r="E81" s="20" t="n">
-        <v>252.3</v>
+        <v>252.1</v>
       </c>
       <c r="F81" s="20" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="G81" s="19" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H81" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I81" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="82">
@@ -3285,19 +3285,19 @@
         <v>250</v>
       </c>
       <c r="E82" s="22" t="n">
-        <v>182.9</v>
+        <v>180.6</v>
       </c>
       <c r="F82" s="22" t="n">
-        <v>80.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G82" s="21" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H82" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I82" s="22" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83">
@@ -3312,19 +3312,19 @@
         <v>508</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>264</v>
+        <v>262.7</v>
       </c>
       <c r="F83" s="17" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="G83" s="16" t="n">
         <v>211</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I83" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="84">
@@ -3344,22 +3344,22 @@
         </is>
       </c>
       <c r="D84" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F84" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I84" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="85">
@@ -3374,19 +3374,19 @@
         <v>81</v>
       </c>
       <c r="E85" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F85" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G85" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H85" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I85" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="86">
@@ -3401,19 +3401,19 @@
         <v>81</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F86" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G86" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H86" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I86" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87">
@@ -3425,22 +3425,22 @@
         </is>
       </c>
       <c r="D87" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E87" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F87" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G87" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I87" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="88">
@@ -3463,19 +3463,19 @@
         <v>379</v>
       </c>
       <c r="E88" s="13" t="n">
-        <v>256.9</v>
+        <v>254.2</v>
       </c>
       <c r="F88" s="13" t="n">
-        <v>33.4</v>
+        <v>36.8</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>32</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I88" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="89">
@@ -3490,19 +3490,19 @@
         <v>379</v>
       </c>
       <c r="E89" s="20" t="n">
-        <v>255.7</v>
+        <v>253.9</v>
       </c>
       <c r="F89" s="20" t="n">
-        <v>32.7</v>
+        <v>35.2</v>
       </c>
       <c r="G89" s="19" t="n">
         <v>50</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I89" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="90">
@@ -3517,19 +3517,19 @@
         <v>379</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>181.1</v>
+        <v>180.1</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>79.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G90" s="21" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H90" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="91">
@@ -3544,19 +3544,19 @@
         <v>379</v>
       </c>
       <c r="E91" s="17" t="n">
-        <v>263.6</v>
+        <v>262.8</v>
       </c>
       <c r="F91" s="17" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="G91" s="16" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="92">
@@ -3576,22 +3576,22 @@
         </is>
       </c>
       <c r="D92" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F92" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I92" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="93">
@@ -3606,19 +3606,19 @@
         <v>81</v>
       </c>
       <c r="E93" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F93" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G93" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H93" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I93" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="94">
@@ -3633,19 +3633,19 @@
         <v>81</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G94" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H94" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="95">
@@ -3657,22 +3657,22 @@
         </is>
       </c>
       <c r="D95" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E95" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F95" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G95" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H95" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I95" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="96">
@@ -3695,19 +3695,19 @@
         <v>379</v>
       </c>
       <c r="E96" s="13" t="n">
-        <v>258.3</v>
+        <v>255.2</v>
       </c>
       <c r="F96" s="13" t="n">
-        <v>30.3</v>
+        <v>35.9</v>
       </c>
       <c r="G96" s="12" t="n">
         <v>36</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I96" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="97">
@@ -3722,19 +3722,19 @@
         <v>379</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>250.9</v>
+        <v>253.5</v>
       </c>
       <c r="F97" s="20" t="n">
-        <v>42.2</v>
+        <v>35.7</v>
       </c>
       <c r="G97" s="19" t="n">
         <v>50</v>
       </c>
       <c r="H97" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I97" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="98">
@@ -3749,19 +3749,19 @@
         <v>508</v>
       </c>
       <c r="E98" s="22" t="n">
-        <v>181.3</v>
+        <v>177.5</v>
       </c>
       <c r="F98" s="22" t="n">
-        <v>79.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I98" s="22" t="n">
-        <v>186.5</v>
+        <v>176</v>
       </c>
     </row>
     <row r="99">
@@ -3776,19 +3776,19 @@
         <v>250</v>
       </c>
       <c r="E99" s="17" t="n">
-        <v>263.4</v>
+        <v>262.1</v>
       </c>
       <c r="F99" s="17" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G99" s="16" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H99" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I99" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100">
@@ -3808,22 +3808,22 @@
         </is>
       </c>
       <c r="D100" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F100" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I100" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="101">
@@ -3838,19 +3838,19 @@
         <v>81</v>
       </c>
       <c r="E101" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F101" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G101" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H101" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I101" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="102">
@@ -3865,19 +3865,19 @@
         <v>81</v>
       </c>
       <c r="E102" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G102" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H102" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I102" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="103">
@@ -3889,22 +3889,22 @@
         </is>
       </c>
       <c r="D103" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E103" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F103" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G103" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H103" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I103" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="104">
@@ -3927,19 +3927,19 @@
         <v>379</v>
       </c>
       <c r="E104" s="13" t="n">
-        <v>256.1</v>
+        <v>254.1</v>
       </c>
       <c r="F104" s="13" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I104" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105">
@@ -3954,19 +3954,19 @@
         <v>379</v>
       </c>
       <c r="E105" s="20" t="n">
-        <v>256</v>
+        <v>252.5</v>
       </c>
       <c r="F105" s="20" t="n">
-        <v>32.5</v>
+        <v>36.7</v>
       </c>
       <c r="G105" s="19" t="n">
         <v>50</v>
       </c>
       <c r="H105" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I105" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106">
@@ -3981,16 +3981,16 @@
         <v>758</v>
       </c>
       <c r="E106" s="22" t="n">
-        <v>182.3</v>
+        <v>181</v>
       </c>
       <c r="F106" s="22" t="n">
-        <v>79.5</v>
+        <v>79.7</v>
       </c>
       <c r="G106" s="21" t="n">
         <v>51</v>
       </c>
       <c r="H106" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I106" s="22" t="n">
         <v>186.5</v>
@@ -4013,22 +4013,22 @@
         </is>
       </c>
       <c r="D107" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F107" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H107" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I107" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="108">
@@ -4043,19 +4043,19 @@
         <v>81</v>
       </c>
       <c r="E108" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F108" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G108" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H108" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I108" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109">
@@ -4070,19 +4070,19 @@
         <v>81</v>
       </c>
       <c r="E109" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F109" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G109" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H109" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I109" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="110">
@@ -4094,22 +4094,22 @@
         </is>
       </c>
       <c r="D110" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F110" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G110" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I110" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -4204,19 +4204,19 @@
         <v>758</v>
       </c>
       <c r="E2" s="13" t="n">
-        <v>258.7</v>
+        <v>257.2</v>
       </c>
       <c r="F2" s="13" t="n">
-        <v>30.1</v>
+        <v>31.7</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H2" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I2" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3">
@@ -4231,7 +4231,7 @@
         <v>758</v>
       </c>
       <c r="E3" s="17" t="n">
-        <v>263.7</v>
+        <v>262.8</v>
       </c>
       <c r="F3" s="17" t="n">
         <v>7.2</v>
@@ -4240,10 +4240,10 @@
         <v>211</v>
       </c>
       <c r="H3" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I3" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4">
@@ -4263,22 +4263,22 @@
         </is>
       </c>
       <c r="D4" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F4" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H4" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I4" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="5">
@@ -4293,19 +4293,19 @@
         <v>81</v>
       </c>
       <c r="E5" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G5" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I5" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6">
@@ -4320,19 +4320,19 @@
         <v>81</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H6" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7">
@@ -4344,22 +4344,22 @@
         </is>
       </c>
       <c r="D7" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I7" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8">
@@ -4382,19 +4382,19 @@
         <v>758</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>257.7</v>
+        <v>257.1</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9">
@@ -4409,19 +4409,19 @@
         <v>250</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>180.1</v>
+        <v>177.4</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>79.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>185.5</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -4436,19 +4436,19 @@
         <v>508</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>263.6</v>
+        <v>263</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11">
@@ -4468,22 +4468,22 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12">
@@ -4498,19 +4498,19 @@
         <v>81</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G12" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H12" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13">
@@ -4525,19 +4525,19 @@
         <v>81</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14">
@@ -4549,22 +4549,22 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F14" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H14" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15">
@@ -4587,7 +4587,7 @@
         <v>758</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>257.4</v>
+        <v>256.2</v>
       </c>
       <c r="F15" s="13" t="n">
         <v>33.4</v>
@@ -4596,10 +4596,10 @@
         <v>32</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16">
@@ -4614,19 +4614,19 @@
         <v>379</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>185.9</v>
+        <v>181.4</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>80.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G16" s="21" t="n">
         <v>51</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="17">
@@ -4641,19 +4641,19 @@
         <v>379</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>263.9</v>
+        <v>262.9</v>
       </c>
       <c r="F17" s="17" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="H17" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I17" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18">
@@ -4673,22 +4673,22 @@
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F18" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I18" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="19">
@@ -4703,19 +4703,19 @@
         <v>81</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F19" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G19" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H19" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I19" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="20">
@@ -4730,19 +4730,19 @@
         <v>81</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
@@ -4754,22 +4754,22 @@
         </is>
       </c>
       <c r="D21" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F21" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G21" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I21" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22">
@@ -4792,19 +4792,19 @@
         <v>758</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>257.7</v>
+        <v>256.5</v>
       </c>
       <c r="F22" s="13" t="n">
-        <v>32.7</v>
+        <v>33.3</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>32</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I22" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23">
@@ -4819,19 +4819,19 @@
         <v>508</v>
       </c>
       <c r="E23" s="22" t="n">
-        <v>182.8</v>
+        <v>182.5</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>80.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>195</v>
+        <v>192.5</v>
       </c>
     </row>
     <row r="24">
@@ -4846,19 +4846,19 @@
         <v>250</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>263.7</v>
+        <v>262.8</v>
       </c>
       <c r="F24" s="17" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="G24" s="16" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I24" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="25">
@@ -4878,22 +4878,22 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I25" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="26">
@@ -4908,19 +4908,19 @@
         <v>81</v>
       </c>
       <c r="E26" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G26" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I26" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="27">
@@ -4935,19 +4935,19 @@
         <v>81</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I27" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="28">
@@ -4959,22 +4959,22 @@
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F28" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G28" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I28" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29">
@@ -4997,19 +4997,19 @@
         <v>758</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>256.9</v>
+        <v>256.4</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>34.4</v>
+        <v>33.9</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>32</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I29" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30">
@@ -5024,19 +5024,19 @@
         <v>758</v>
       </c>
       <c r="E30" s="22" t="n">
-        <v>183.5</v>
+        <v>181.6</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>79.8</v>
+        <v>79</v>
       </c>
       <c r="G30" s="21" t="n">
         <v>51</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31">
@@ -5056,22 +5056,22 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I31" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="32">
@@ -5086,19 +5086,19 @@
         <v>81</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F32" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G32" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H32" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I32" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="33">
@@ -5113,19 +5113,19 @@
         <v>81</v>
       </c>
       <c r="E33" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H33" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I33" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34">
@@ -5137,22 +5137,22 @@
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F34" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I34" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35">
@@ -5175,19 +5175,19 @@
         <v>508</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>257.8</v>
+        <v>257.4</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>32</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I35" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36">
@@ -5202,19 +5202,19 @@
         <v>250</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>257.4</v>
+        <v>255.9</v>
       </c>
       <c r="F36" s="20" t="n">
-        <v>28.8</v>
+        <v>33.1</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I36" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="37">
@@ -5229,7 +5229,7 @@
         <v>758</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>263.8</v>
+        <v>262.9</v>
       </c>
       <c r="F37" s="17" t="n">
         <v>7</v>
@@ -5238,10 +5238,10 @@
         <v>211</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I37" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="38">
@@ -5261,22 +5261,22 @@
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F38" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="39">
@@ -5291,19 +5291,19 @@
         <v>81</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F39" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G39" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I39" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="40">
@@ -5318,19 +5318,19 @@
         <v>81</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H40" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41">
@@ -5342,22 +5342,22 @@
         </is>
       </c>
       <c r="D41" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E41" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F41" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I41" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="42">
@@ -5380,19 +5380,19 @@
         <v>508</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>257.1</v>
+        <v>258</v>
       </c>
       <c r="F42" s="13" t="n">
-        <v>34.5</v>
+        <v>31.5</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>32</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I42" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="43">
@@ -5407,19 +5407,19 @@
         <v>250</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>252.9</v>
+        <v>256.3</v>
       </c>
       <c r="F43" s="20" t="n">
-        <v>39.2</v>
+        <v>30.7</v>
       </c>
       <c r="G43" s="19" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I43" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44">
@@ -5434,19 +5434,19 @@
         <v>250</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>190</v>
+        <v>178.1</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>78.59999999999999</v>
+        <v>80</v>
       </c>
       <c r="G44" s="21" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H44" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>225</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45">
@@ -5461,19 +5461,19 @@
         <v>508</v>
       </c>
       <c r="E45" s="17" t="n">
-        <v>264.1</v>
+        <v>262.8</v>
       </c>
       <c r="F45" s="17" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I45" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="46">
@@ -5493,22 +5493,22 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F46" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I46" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="47">
@@ -5523,19 +5523,19 @@
         <v>81</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F47" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G47" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I47" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="48">
@@ -5550,19 +5550,19 @@
         <v>81</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G48" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H48" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49">
@@ -5574,22 +5574,22 @@
         </is>
       </c>
       <c r="D49" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E49" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F49" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G49" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I49" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="50">
@@ -5612,19 +5612,19 @@
         <v>508</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>257.9</v>
+        <v>258.5</v>
       </c>
       <c r="F50" s="13" t="n">
-        <v>32.2</v>
+        <v>28.3</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>36</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I50" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51">
@@ -5639,19 +5639,19 @@
         <v>250</v>
       </c>
       <c r="E51" s="20" t="n">
-        <v>257.2</v>
+        <v>254.9</v>
       </c>
       <c r="F51" s="20" t="n">
-        <v>28.5</v>
+        <v>33</v>
       </c>
       <c r="G51" s="19" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="H51" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I51" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="52">
@@ -5666,19 +5666,19 @@
         <v>379</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>178.3</v>
+        <v>188.4</v>
       </c>
       <c r="F52" s="22" t="n">
-        <v>80.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G52" s="21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H52" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>178</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53">
@@ -5693,19 +5693,19 @@
         <v>379</v>
       </c>
       <c r="E53" s="17" t="n">
-        <v>264.1</v>
+        <v>263.1</v>
       </c>
       <c r="F53" s="17" t="n">
         <v>6.1</v>
       </c>
       <c r="G53" s="16" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I53" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54">
@@ -5725,22 +5725,22 @@
         </is>
       </c>
       <c r="D54" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F54" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I54" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="55">
@@ -5755,19 +5755,19 @@
         <v>81</v>
       </c>
       <c r="E55" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F55" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G55" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H55" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I55" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="56">
@@ -5782,19 +5782,19 @@
         <v>81</v>
       </c>
       <c r="E56" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F56" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G56" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H56" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I56" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57">
@@ -5806,22 +5806,22 @@
         </is>
       </c>
       <c r="D57" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E57" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F57" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G57" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I57" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="58">
@@ -5844,19 +5844,19 @@
         <v>508</v>
       </c>
       <c r="E58" s="13" t="n">
-        <v>258.3</v>
+        <v>257</v>
       </c>
       <c r="F58" s="13" t="n">
-        <v>31</v>
+        <v>31.9</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I58" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="59">
@@ -5871,19 +5871,19 @@
         <v>250</v>
       </c>
       <c r="E59" s="20" t="n">
-        <v>254.3</v>
+        <v>255</v>
       </c>
       <c r="F59" s="20" t="n">
-        <v>37.8</v>
+        <v>33.5</v>
       </c>
       <c r="G59" s="19" t="n">
         <v>61</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I59" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="60">
@@ -5898,19 +5898,19 @@
         <v>508</v>
       </c>
       <c r="E60" s="22" t="n">
-        <v>179</v>
+        <v>181.3</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>79.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G60" s="21" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H60" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I60" s="22" t="n">
-        <v>173.5</v>
+        <v>186.5</v>
       </c>
     </row>
     <row r="61">
@@ -5925,19 +5925,19 @@
         <v>250</v>
       </c>
       <c r="E61" s="17" t="n">
-        <v>263.3</v>
+        <v>262.3</v>
       </c>
       <c r="F61" s="17" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="G61" s="16" t="n">
         <v>215</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I61" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="62">
@@ -5957,22 +5957,22 @@
         </is>
       </c>
       <c r="D62" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E62" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F62" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I62" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="63">
@@ -5987,19 +5987,19 @@
         <v>81</v>
       </c>
       <c r="E63" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F63" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G63" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H63" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I63" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="64">
@@ -6014,19 +6014,19 @@
         <v>81</v>
       </c>
       <c r="E64" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F64" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G64" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H64" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I64" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="65">
@@ -6038,22 +6038,22 @@
         </is>
       </c>
       <c r="D65" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E65" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F65" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G65" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I65" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="66">
@@ -6076,19 +6076,19 @@
         <v>508</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>257.7</v>
+        <v>256.8</v>
       </c>
       <c r="F66" s="13" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G66" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="G66" s="12" t="n">
-        <v>36</v>
-      </c>
       <c r="H66" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I66" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="67">
@@ -6103,19 +6103,19 @@
         <v>250</v>
       </c>
       <c r="E67" s="20" t="n">
-        <v>254.1</v>
+        <v>253.2</v>
       </c>
       <c r="F67" s="20" t="n">
-        <v>36.1</v>
+        <v>36.3</v>
       </c>
       <c r="G67" s="19" t="n">
         <v>50</v>
       </c>
       <c r="H67" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I67" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="68">
@@ -6130,19 +6130,19 @@
         <v>758</v>
       </c>
       <c r="E68" s="22" t="n">
-        <v>182.7</v>
+        <v>183.5</v>
       </c>
       <c r="F68" s="22" t="n">
         <v>79.7</v>
       </c>
       <c r="G68" s="21" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H68" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I68" s="22" t="n">
-        <v>187.5</v>
+        <v>194.5</v>
       </c>
     </row>
     <row r="69">
@@ -6162,22 +6162,22 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F69" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I69" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="70">
@@ -6192,19 +6192,19 @@
         <v>81</v>
       </c>
       <c r="E70" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F70" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G70" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H70" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="71">
@@ -6219,19 +6219,19 @@
         <v>81</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F71" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G71" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H71" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I71" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="72">
@@ -6243,22 +6243,22 @@
         </is>
       </c>
       <c r="D72" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E72" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F72" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G72" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I72" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73">
@@ -6281,19 +6281,19 @@
         <v>379</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>259.6</v>
+        <v>257.2</v>
       </c>
       <c r="F73" s="13" t="n">
-        <v>27.1</v>
+        <v>32.9</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I73" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="74">
@@ -6308,19 +6308,19 @@
         <v>379</v>
       </c>
       <c r="E74" s="20" t="n">
-        <v>255.3</v>
+        <v>252.3</v>
       </c>
       <c r="F74" s="20" t="n">
-        <v>34.1</v>
+        <v>36.9</v>
       </c>
       <c r="G74" s="19" t="n">
         <v>72</v>
       </c>
       <c r="H74" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I74" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="75">
@@ -6335,19 +6335,19 @@
         <v>758</v>
       </c>
       <c r="E75" s="17" t="n">
-        <v>263.8</v>
+        <v>262.8</v>
       </c>
       <c r="F75" s="17" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="G75" s="16" t="n">
         <v>211</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I75" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="76">
@@ -6367,22 +6367,22 @@
         </is>
       </c>
       <c r="D76" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F76" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I76" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="77">
@@ -6397,19 +6397,19 @@
         <v>81</v>
       </c>
       <c r="E77" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F77" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G77" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H77" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I77" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="78">
@@ -6424,19 +6424,19 @@
         <v>81</v>
       </c>
       <c r="E78" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F78" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G78" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H78" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I78" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="79">
@@ -6448,22 +6448,22 @@
         </is>
       </c>
       <c r="D79" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E79" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F79" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G79" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H79" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I79" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="80">
@@ -6486,19 +6486,19 @@
         <v>379</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>256.4</v>
+        <v>254</v>
       </c>
       <c r="F80" s="13" t="n">
-        <v>34.3</v>
+        <v>38.8</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I80" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="81">
@@ -6513,19 +6513,19 @@
         <v>379</v>
       </c>
       <c r="E81" s="20" t="n">
-        <v>252.3</v>
+        <v>252.1</v>
       </c>
       <c r="F81" s="20" t="n">
-        <v>38.7</v>
+        <v>38.4</v>
       </c>
       <c r="G81" s="19" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="H81" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I81" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="82">
@@ -6540,19 +6540,19 @@
         <v>250</v>
       </c>
       <c r="E82" s="22" t="n">
-        <v>182.9</v>
+        <v>180.6</v>
       </c>
       <c r="F82" s="22" t="n">
-        <v>80.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G82" s="21" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H82" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I82" s="22" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83">
@@ -6567,19 +6567,19 @@
         <v>508</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>264</v>
+        <v>262.7</v>
       </c>
       <c r="F83" s="17" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="G83" s="16" t="n">
         <v>211</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I83" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="84">
@@ -6599,22 +6599,22 @@
         </is>
       </c>
       <c r="D84" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F84" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I84" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="85">
@@ -6629,19 +6629,19 @@
         <v>81</v>
       </c>
       <c r="E85" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F85" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G85" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H85" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I85" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="86">
@@ -6656,19 +6656,19 @@
         <v>81</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F86" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G86" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H86" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I86" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87">
@@ -6680,22 +6680,22 @@
         </is>
       </c>
       <c r="D87" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E87" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F87" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G87" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I87" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="88">
@@ -6718,19 +6718,19 @@
         <v>379</v>
       </c>
       <c r="E88" s="13" t="n">
-        <v>256.9</v>
+        <v>254.2</v>
       </c>
       <c r="F88" s="13" t="n">
-        <v>33.4</v>
+        <v>36.8</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>32</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I88" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="89">
@@ -6745,19 +6745,19 @@
         <v>379</v>
       </c>
       <c r="E89" s="20" t="n">
-        <v>255.7</v>
+        <v>253.9</v>
       </c>
       <c r="F89" s="20" t="n">
-        <v>32.7</v>
+        <v>35.2</v>
       </c>
       <c r="G89" s="19" t="n">
         <v>50</v>
       </c>
       <c r="H89" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I89" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="90">
@@ -6772,19 +6772,19 @@
         <v>379</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>181.1</v>
+        <v>180.1</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>79.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G90" s="21" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H90" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="91">
@@ -6799,19 +6799,19 @@
         <v>379</v>
       </c>
       <c r="E91" s="17" t="n">
-        <v>263.6</v>
+        <v>262.8</v>
       </c>
       <c r="F91" s="17" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="G91" s="16" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="H91" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I91" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="92">
@@ -6831,22 +6831,22 @@
         </is>
       </c>
       <c r="D92" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E92" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F92" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I92" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="93">
@@ -6861,19 +6861,19 @@
         <v>81</v>
       </c>
       <c r="E93" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F93" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G93" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H93" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I93" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="94">
@@ -6888,19 +6888,19 @@
         <v>81</v>
       </c>
       <c r="E94" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G94" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H94" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="95">
@@ -6912,22 +6912,22 @@
         </is>
       </c>
       <c r="D95" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E95" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F95" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G95" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H95" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I95" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="96">
@@ -6950,19 +6950,19 @@
         <v>379</v>
       </c>
       <c r="E96" s="13" t="n">
-        <v>258.3</v>
+        <v>255.2</v>
       </c>
       <c r="F96" s="13" t="n">
-        <v>30.3</v>
+        <v>35.9</v>
       </c>
       <c r="G96" s="12" t="n">
         <v>36</v>
       </c>
       <c r="H96" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I96" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="97">
@@ -6977,19 +6977,19 @@
         <v>379</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>250.9</v>
+        <v>253.5</v>
       </c>
       <c r="F97" s="20" t="n">
-        <v>42.2</v>
+        <v>35.7</v>
       </c>
       <c r="G97" s="19" t="n">
         <v>50</v>
       </c>
       <c r="H97" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I97" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="98">
@@ -7004,19 +7004,19 @@
         <v>508</v>
       </c>
       <c r="E98" s="22" t="n">
-        <v>181.3</v>
+        <v>177.5</v>
       </c>
       <c r="F98" s="22" t="n">
-        <v>79.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I98" s="22" t="n">
-        <v>186.5</v>
+        <v>176</v>
       </c>
     </row>
     <row r="99">
@@ -7031,19 +7031,19 @@
         <v>250</v>
       </c>
       <c r="E99" s="17" t="n">
-        <v>263.4</v>
+        <v>262.1</v>
       </c>
       <c r="F99" s="17" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G99" s="16" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H99" s="16" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I99" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100">
@@ -7063,22 +7063,22 @@
         </is>
       </c>
       <c r="D100" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F100" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H100" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I100" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="101">
@@ -7093,19 +7093,19 @@
         <v>81</v>
       </c>
       <c r="E101" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F101" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G101" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H101" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I101" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="102">
@@ -7120,19 +7120,19 @@
         <v>81</v>
       </c>
       <c r="E102" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G102" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H102" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I102" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="103">
@@ -7144,22 +7144,22 @@
         </is>
       </c>
       <c r="D103" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E103" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F103" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G103" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H103" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I103" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="104">
@@ -7182,19 +7182,19 @@
         <v>379</v>
       </c>
       <c r="E104" s="13" t="n">
-        <v>256.1</v>
+        <v>254.1</v>
       </c>
       <c r="F104" s="13" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="H104" s="12" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I104" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105">
@@ -7209,19 +7209,19 @@
         <v>379</v>
       </c>
       <c r="E105" s="20" t="n">
-        <v>256</v>
+        <v>252.5</v>
       </c>
       <c r="F105" s="20" t="n">
-        <v>32.5</v>
+        <v>36.7</v>
       </c>
       <c r="G105" s="19" t="n">
         <v>50</v>
       </c>
       <c r="H105" s="19" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I105" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="106">
@@ -7236,16 +7236,16 @@
         <v>758</v>
       </c>
       <c r="E106" s="22" t="n">
-        <v>182.3</v>
+        <v>181</v>
       </c>
       <c r="F106" s="22" t="n">
-        <v>79.5</v>
+        <v>79.7</v>
       </c>
       <c r="G106" s="21" t="n">
         <v>51</v>
       </c>
       <c r="H106" s="21" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I106" s="22" t="n">
         <v>186.5</v>
@@ -7268,22 +7268,22 @@
         </is>
       </c>
       <c r="D107" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>579.6</v>
+        <v>602.9</v>
       </c>
       <c r="F107" s="13" t="n">
-        <v>211.2</v>
+        <v>328.5</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="H107" s="12" t="n">
-        <v>1027</v>
+        <v>2705</v>
       </c>
       <c r="I107" s="13" t="n">
-        <v>569</v>
+        <v>592</v>
       </c>
     </row>
     <row r="108">
@@ -7298,19 +7298,19 @@
         <v>81</v>
       </c>
       <c r="E108" s="20" t="n">
-        <v>357.7</v>
+        <v>380.8</v>
       </c>
       <c r="F108" s="20" t="n">
-        <v>120.3</v>
+        <v>147</v>
       </c>
       <c r="G108" s="19" t="n">
         <v>53</v>
       </c>
       <c r="H108" s="19" t="n">
-        <v>615</v>
+        <v>807</v>
       </c>
       <c r="I108" s="20" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109">
@@ -7325,19 +7325,19 @@
         <v>81</v>
       </c>
       <c r="E109" s="22" t="n">
-        <v>313.9</v>
+        <v>292.3</v>
       </c>
       <c r="F109" s="22" t="n">
-        <v>345.2</v>
+        <v>226.6</v>
       </c>
       <c r="G109" s="21" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H109" s="21" t="n">
-        <v>2037</v>
+        <v>1098</v>
       </c>
       <c r="I109" s="22" t="n">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="110">
@@ -7349,22 +7349,22 @@
         </is>
       </c>
       <c r="D110" s="16" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E110" s="17" t="n">
-        <v>303.4</v>
+        <v>296.3</v>
       </c>
       <c r="F110" s="17" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="G110" s="16" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H110" s="16" t="n">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I110" s="17" t="n">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -7445,23 +7445,23 @@
         </is>
       </c>
       <c r="C2" s="12" t="n">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D2" s="13" t="n">
-        <v>549.5</v>
+        <v>547.5</v>
       </c>
       <c r="E2" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F2" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G2" s="24" t="n">
-        <v>0.7489130434782608</v>
+        <v>0.7483731019522777</v>
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7480,20 +7480,20 @@
         <v>162</v>
       </c>
       <c r="D3" s="20" t="n">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="E3" s="20" t="n">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="F3" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G3" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7512,20 +7512,20 @@
         <v>162</v>
       </c>
       <c r="D4" s="22" t="n">
-        <v>202</v>
+        <v>212.5</v>
       </c>
       <c r="E4" s="22" t="n">
-        <v>202</v>
+        <v>212.5</v>
       </c>
       <c r="F4" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>0</v>
+        <v>0.006172839506172839</v>
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7541,23 +7541,23 @@
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>294</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>0.6919739696312365</v>
+        <v>0.7076086956521739</v>
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7573,23 +7573,23 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>558.5</v>
+        <v>565.5</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>0.7456521739130435</v>
+        <v>0.7505422993492408</v>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7608,20 +7608,20 @@
         <v>162</v>
       </c>
       <c r="D7" s="20" t="n">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="E7" s="20" t="n">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G7" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7640,20 +7640,20 @@
         <v>412</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F8" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>0.220873786407767</v>
+        <v>0.2257281553398058</v>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7669,23 +7669,23 @@
         </is>
       </c>
       <c r="C9" s="16" t="n">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.6537313432835821</v>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7701,23 +7701,23 @@
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>560</v>
+        <v>550.5</v>
       </c>
       <c r="E10" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>0.7456521739130435</v>
+        <v>0.7440347071583514</v>
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7736,20 +7736,20 @@
         <v>162</v>
       </c>
       <c r="D11" s="20" t="n">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="E11" s="20" t="n">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G11" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7768,20 +7768,20 @@
         <v>541</v>
       </c>
       <c r="D12" s="22" t="n">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G12" s="26" t="n">
-        <v>0.2828096118299446</v>
+        <v>0.2606284658040666</v>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7797,23 +7797,23 @@
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D13" s="17" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.6095764272559853</v>
+        <v>0.6099815157116451</v>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7829,23 +7829,23 @@
         </is>
       </c>
       <c r="C14" s="12" t="n">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D14" s="13" t="n">
-        <v>551.5</v>
+        <v>548</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F14" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G14" s="24" t="n">
-        <v>0.7456521739130435</v>
+        <v>0.7472885032537961</v>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7864,20 +7864,20 @@
         <v>162</v>
       </c>
       <c r="D15" s="20" t="n">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="E15" s="20" t="n">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="F15" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G15" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7896,20 +7896,20 @@
         <v>670</v>
       </c>
       <c r="D16" s="22" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F16" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>0.2955223880597015</v>
+        <v>0.2940298507462686</v>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7925,23 +7925,23 @@
         </is>
       </c>
       <c r="C17" s="16" t="n">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D17" s="17" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F17" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G17" s="24" t="n">
-        <v>0.5193236714975845</v>
+        <v>0.5266990291262136</v>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7957,23 +7957,23 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>560.5</v>
+        <v>558.5</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F18" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G18" s="24" t="n">
-        <v>0.7445652173913043</v>
+        <v>0.7483731019522777</v>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -7992,20 +7992,20 @@
         <v>162</v>
       </c>
       <c r="D19" s="20" t="n">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="E19" s="20" t="n">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G19" s="25" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8024,20 +8024,20 @@
         <v>920</v>
       </c>
       <c r="D20" s="22" t="n">
-        <v>194.5</v>
+        <v>191.5</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>194.5</v>
+        <v>191.5</v>
       </c>
       <c r="F20" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>0.3173913043478261</v>
+        <v>0.3130434782608696</v>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8053,23 +8053,23 @@
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D21" s="17" t="n">
-        <v>301</v>
+        <v>294.5</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>301</v>
+        <v>294.5</v>
       </c>
       <c r="F21" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G21" s="25" t="n">
-        <v>0.006097560975609756</v>
+        <v>0.01851851851851852</v>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8085,23 +8085,23 @@
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D22" s="13" t="n">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="E22" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F22" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G22" s="24" t="n">
-        <v>0.6865671641791045</v>
+        <v>0.6964285714285714</v>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8120,20 +8120,20 @@
         <v>412</v>
       </c>
       <c r="D23" s="20" t="n">
-        <v>371</v>
+        <v>387.5</v>
       </c>
       <c r="E23" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F23" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G23" s="24" t="n">
-        <v>0.5145631067961165</v>
+        <v>0.5218446601941747</v>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8152,20 +8152,20 @@
         <v>162</v>
       </c>
       <c r="D24" s="22" t="n">
-        <v>202</v>
+        <v>212.5</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>202</v>
+        <v>212.5</v>
       </c>
       <c r="F24" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G24" s="25" t="n">
-        <v>0</v>
+        <v>0.006172839506172839</v>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8181,23 +8181,23 @@
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D25" s="17" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F25" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G25" s="24" t="n">
-        <v>0.6919739696312365</v>
+        <v>0.7119565217391305</v>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8213,23 +8213,23 @@
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F26" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G26" s="24" t="n">
-        <v>0.682089552238806</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8248,20 +8248,20 @@
         <v>412</v>
       </c>
       <c r="D27" s="20" t="n">
-        <v>377.5</v>
+        <v>385.5</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F27" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G27" s="24" t="n">
-        <v>0.5072815533980582</v>
+        <v>0.5194174757281553</v>
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8280,20 +8280,20 @@
         <v>412</v>
       </c>
       <c r="D28" s="22" t="n">
-        <v>210</v>
+        <v>192.5</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>210</v>
+        <v>192.5</v>
       </c>
       <c r="F28" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G28" s="26" t="n">
-        <v>0.2524271844660194</v>
+        <v>0.2111650485436893</v>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8309,23 +8309,23 @@
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D29" s="17" t="n">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F29" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G29" s="24" t="n">
-        <v>0.6577380952380952</v>
+        <v>0.6492537313432836</v>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8341,23 +8341,23 @@
         </is>
       </c>
       <c r="C30" s="12" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D30" s="13" t="n">
-        <v>550.5</v>
+        <v>546.5</v>
       </c>
       <c r="E30" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F30" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G30" s="24" t="n">
-        <v>0.6865671641791045</v>
+        <v>0.6934523809523809</v>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8376,20 +8376,20 @@
         <v>412</v>
       </c>
       <c r="D31" s="20" t="n">
-        <v>389.5</v>
+        <v>372</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F31" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G31" s="24" t="n">
-        <v>0.5218446601941747</v>
+        <v>0.5121359223300971</v>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8408,20 +8408,20 @@
         <v>541</v>
       </c>
       <c r="D32" s="22" t="n">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="E32" s="22" t="n">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="F32" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G32" s="26" t="n">
-        <v>0.2513863216266174</v>
+        <v>0.2994454713493531</v>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8437,23 +8437,23 @@
         </is>
       </c>
       <c r="C33" s="16" t="n">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D33" s="17" t="n">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F33" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G33" s="24" t="n">
-        <v>0.5874769797421732</v>
+        <v>0.6062846580406654</v>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8469,23 +8469,23 @@
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D34" s="13" t="n">
-        <v>558.5</v>
+        <v>569</v>
       </c>
       <c r="E34" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F34" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G34" s="24" t="n">
-        <v>0.6925373134328359</v>
+        <v>0.6919642857142857</v>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8504,20 +8504,20 @@
         <v>412</v>
       </c>
       <c r="D35" s="20" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F35" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G35" s="24" t="n">
-        <v>0.5097087378640777</v>
+        <v>0.5145631067961165</v>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8536,20 +8536,20 @@
         <v>670</v>
       </c>
       <c r="D36" s="22" t="n">
-        <v>185</v>
+        <v>191.5</v>
       </c>
       <c r="E36" s="22" t="n">
-        <v>185</v>
+        <v>191.5</v>
       </c>
       <c r="F36" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G36" s="26" t="n">
-        <v>0.2835820895522388</v>
+        <v>0.2880597014925373</v>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8565,23 +8565,23 @@
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D37" s="17" t="n">
         <v>295</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F37" s="23" t="n">
-        <v>266</v>
-      </c>
-      <c r="G37" s="26" t="n">
-        <v>0.5</v>
+        <v>265</v>
+      </c>
+      <c r="G37" s="24" t="n">
+        <v>0.529126213592233</v>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8597,23 +8597,23 @@
         </is>
       </c>
       <c r="C38" s="12" t="n">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="D38" s="13" t="n">
-        <v>561.5</v>
+        <v>555.5</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F38" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G38" s="24" t="n">
-        <v>0.6835820895522388</v>
+        <v>0.6919642857142857</v>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8632,20 +8632,20 @@
         <v>412</v>
       </c>
       <c r="D39" s="20" t="n">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E39" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F39" s="23" t="n">
-        <v>266</v>
-      </c>
-      <c r="G39" s="24" t="n">
-        <v>0.5145631067961165</v>
+        <v>265</v>
+      </c>
+      <c r="G39" s="26" t="n">
+        <v>0.5</v>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8664,20 +8664,20 @@
         <v>920</v>
       </c>
       <c r="D40" s="22" t="n">
-        <v>189.5</v>
+        <v>198</v>
       </c>
       <c r="E40" s="22" t="n">
-        <v>189.5</v>
+        <v>198</v>
       </c>
       <c r="F40" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G40" s="26" t="n">
-        <v>0.3152173913043478</v>
+        <v>0.3304347826086956</v>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8693,23 +8693,23 @@
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D41" s="17" t="n">
-        <v>301</v>
+        <v>294.5</v>
       </c>
       <c r="E41" s="17" t="n">
-        <v>301</v>
+        <v>294.5</v>
       </c>
       <c r="F41" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G41" s="25" t="n">
-        <v>0.006097560975609756</v>
+        <v>0.01851851851851852</v>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8725,23 +8725,23 @@
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F42" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G42" s="24" t="n">
-        <v>0.6487985212569316</v>
+        <v>0.6408839779005525</v>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8760,20 +8760,20 @@
         <v>541</v>
       </c>
       <c r="D43" s="20" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E43" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F43" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G43" s="24" t="n">
-        <v>0.5914972273567468</v>
+        <v>0.5785582255083179</v>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8792,20 +8792,20 @@
         <v>162</v>
       </c>
       <c r="D44" s="22" t="n">
-        <v>202</v>
+        <v>212.5</v>
       </c>
       <c r="E44" s="22" t="n">
-        <v>202</v>
+        <v>212.5</v>
       </c>
       <c r="F44" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G44" s="25" t="n">
-        <v>0</v>
+        <v>0.006172839506172839</v>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8821,23 +8821,23 @@
         </is>
       </c>
       <c r="C45" s="16" t="n">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="D45" s="17" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E45" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F45" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G45" s="24" t="n">
-        <v>0.693058568329718</v>
+        <v>0.7130434782608696</v>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8853,23 +8853,23 @@
         </is>
       </c>
       <c r="C46" s="12" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>527</v>
+        <v>550</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F46" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G46" s="24" t="n">
-        <v>0.6192236598890942</v>
+        <v>0.6243093922651933</v>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8891,17 +8891,17 @@
         <v>372</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F47" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G47" s="24" t="n">
         <v>0.5841035120147874</v>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8920,20 +8920,20 @@
         <v>412</v>
       </c>
       <c r="D48" s="22" t="n">
-        <v>194.5</v>
+        <v>194</v>
       </c>
       <c r="E48" s="22" t="n">
-        <v>194.5</v>
+        <v>194</v>
       </c>
       <c r="F48" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G48" s="26" t="n">
-        <v>0.2354368932038835</v>
+        <v>0.2305825242718447</v>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8949,23 +8949,23 @@
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="D49" s="17" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E49" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F49" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G49" s="24" t="n">
-        <v>0.6502976190476191</v>
+        <v>0.6492537313432836</v>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -8981,23 +8981,23 @@
         </is>
       </c>
       <c r="C50" s="12" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F50" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G50" s="24" t="n">
-        <v>0.6303142329020333</v>
+        <v>0.6187845303867403</v>
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -9016,20 +9016,20 @@
         <v>541</v>
       </c>
       <c r="D51" s="20" t="n">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="E51" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F51" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G51" s="24" t="n">
         <v>0.5859519408502772</v>
       </c>
       <c r="H51" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -9048,20 +9048,20 @@
         <v>541</v>
       </c>
       <c r="D52" s="22" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F52" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G52" s="26" t="n">
-        <v>0.2717190388170055</v>
+        <v>0.2606284658040666</v>
       </c>
       <c r="H52" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -9077,23 +9077,23 @@
         </is>
       </c>
       <c r="C53" s="16" t="n">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D53" s="17" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E53" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F53" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G53" s="24" t="n">
-        <v>0.58195211786372</v>
+        <v>0.5970425138632163</v>
       </c>
       <c r="H53" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -9109,23 +9109,23 @@
         </is>
       </c>
       <c r="C54" s="12" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D54" s="13" t="n">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="E54" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F54" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G54" s="24" t="n">
-        <v>0.6321626617375231</v>
+        <v>0.6335174953959485</v>
       </c>
       <c r="H54" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -9144,20 +9144,20 @@
         <v>541</v>
       </c>
       <c r="D55" s="20" t="n">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="E55" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F55" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G55" s="24" t="n">
-        <v>0.5785582255083179</v>
+        <v>0.5859519408502772</v>
       </c>
       <c r="H55" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -9176,20 +9176,20 @@
         <v>670</v>
       </c>
       <c r="D56" s="22" t="n">
-        <v>191</v>
+        <v>185.5</v>
       </c>
       <c r="E56" s="22" t="n">
-        <v>191</v>
+        <v>185.5</v>
       </c>
       <c r="F56" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G56" s="26" t="n">
-        <v>0.282089552238806</v>
+        <v>0.2761194029850746</v>
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -9205,23 +9205,23 @@
         </is>
       </c>
       <c r="C57" s="16" t="n">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D57" s="17" t="n">
         <v>295</v>
       </c>
       <c r="E57" s="17" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F57" s="23" t="n">
-        <v>266</v>
-      </c>
-      <c r="G57" s="26" t="n">
-        <v>0.4975845410628019</v>
+        <v>265</v>
+      </c>
+      <c r="G57" s="24" t="n">
+        <v>0.5218446601941747</v>
       </c>
       <c r="H57" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -9237,23 +9237,23 @@
         </is>
       </c>
       <c r="C58" s="12" t="n">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D58" s="13" t="n">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="E58" s="13" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F58" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G58" s="24" t="n">
-        <v>0.6321626617375231</v>
+        <v>0.6114180478821363</v>
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -9272,20 +9272,20 @@
         <v>541</v>
       </c>
       <c r="D59" s="20" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E59" s="20" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F59" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G59" s="24" t="n">
-        <v>0.5933456561922366</v>
+        <v>0.5637707948243993</v>
       </c>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -9304,20 +9304,20 @@
         <v>920</v>
       </c>
       <c r="D60" s="22" t="n">
-        <v>187.5</v>
+        <v>190.5</v>
       </c>
       <c r="E60" s="22" t="n">
-        <v>187.5</v>
+        <v>190.5</v>
       </c>
       <c r="F60" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G60" s="26" t="n">
-        <v>0.316304347826087</v>
+        <v>0.3228260869565218</v>
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
@@ -9333,23 +9333,23 @@
         </is>
       </c>
       <c r="C61" s="16" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D61" s="17" t="n">
-        <v>301</v>
+        <v>294.5</v>
       </c>
       <c r="E61" s="17" t="n">
-        <v>301</v>
+        <v>294.5</v>
       </c>
       <c r="F61" s="23" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G61" s="25" t="n">
-        <v>0.006097560975609756</v>
+        <v>0.01851851851851852</v>
       </c>
       <c r="H61" s="14" t="inlineStr">
         <is>
-          <t>mean of HF (train only) across all sheets (AI-F=296, AI-R=379, HF=267, HR=568)</t>
+          <t>mean of HF (train only) across all sheets (AI-F=297, AI-R=372, HF=266, HR=565)</t>
         </is>
       </c>
     </row>
